--- a/data/trans_dic/P02E$ssociales-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P02E$ssociales-Habitat-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con ayuda al cuidado por parte de, al menos, una persona externa que es profesional de los servicios Sociales o sanitarios</t>
+          <t>Hogares con ayuda al cuidado por parte de, al menos, una persona externa que es profesional de los servicios Sociales o sanitarios (tasa de respuesta: 96,71%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,76</t>
+          <t>0,0; 3,74</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,96; 5,33</t>
+          <t>0,95; 5,62</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,67; 6,11</t>
+          <t>0,68; 6,22</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,54</t>
+          <t>0,0; 3,64</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,65; 3,64</t>
+          <t>0,66; 3,66</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,02</t>
+          <t>0,0; 3,39</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,28; 2,23</t>
+          <t>0,28; 2,37</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,98; 3,45</t>
+          <t>0,98; 3,46</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,78; 3,59</t>
+          <t>0,57; 3,42</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0; 1,06</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,37; 3,62</t>
+          <t>0,37; 3,36</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,5</t>
+          <t>0,0; 2,54</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,67</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,7; 3,36</t>
+          <t>0,89; 3,35</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,26; 2,85</t>
+          <t>0,27; 2,63</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,85; 2,77</t>
+          <t>0,84; 2,89</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,33; 2,13</t>
+          <t>0,33; 2,04</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 1,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,82</t>
+          <t>0,0; 2,86</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,62; 5,91</t>
+          <t>0,62; 5,81</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,3</t>
+          <t>0,0; 2,25</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,3</t>
+          <t>0,0; 1,6</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,78</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,39</t>
+          <t>0,0; 1,55</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,62</t>
+          <t>0,17; 1,48</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,24; 2,32</t>
+          <t>0,24; 2,27</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,56</t>
+          <t>0,0; 2,61</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,69; 3,79</t>
+          <t>0,72; 4,01</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,79</t>
+          <t>0,0; 2,63</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,39</t>
+          <t>0,0; 2,12</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,51; 2,88</t>
+          <t>0,5; 2,83</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,68; 3,83</t>
+          <t>0,67; 3,82</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,65</t>
+          <t>0,19; 1,84</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,76; 2,75</t>
+          <t>0,75; 2,87</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,61; 2,7</t>
+          <t>0,58; 2,54</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,92</t>
+          <t>0,0; 1,04</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,94; 2,54</t>
+          <t>0,95; 2,67</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,69; 2,46</t>
+          <t>0,67; 2,51</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,07</t>
+          <t>0,1; 1,07</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,81; 1,96</t>
+          <t>0,81; 2,03</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,47; 1,7</t>
+          <t>0,48; 1,72</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,18; 0,84</t>
+          <t>0,18; 0,82</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,03; 1,99</t>
+          <t>1,01; 2,0</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,68; 1,66</t>
+          <t>0,73; 1,72</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con ayuda al cuidado por parte de, al menos, una persona externa que es profesional de los servicios Sociales o sanitarios</t>
+          <t>Hogares con ayuda al cuidado por parte de, al menos, una persona externa que es profesional de los servicios Sociales o sanitarios (tasa de respuesta: 96,71%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1417,47 +1417,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 4929</t>
+          <t>0; 4908</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1912; 10585</t>
+          <t>1887; 11163</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1073; 9796</t>
+          <t>1087; 9982</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 7792</t>
+          <t>0; 8006</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1925; 10874</t>
+          <t>1961; 10923</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 5940</t>
+          <t>0; 6664</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>971; 7835</t>
+          <t>970; 8335</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>4878; 17147</t>
+          <t>4890; 17205</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2775; 12831</t>
+          <t>2020; 12216</t>
         </is>
       </c>
     </row>
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 2087</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1119; 11006</t>
+          <t>1123; 10217</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 5948</t>
+          <t>0; 6040</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 2047</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3215; 15388</t>
+          <t>4077; 15358</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>948; 10221</t>
+          <t>956; 9432</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 2068</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6498; 21074</t>
+          <t>6374; 22028</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1972; 12693</t>
+          <t>1982; 12134</t>
         </is>
       </c>
     </row>
@@ -1743,47 +1743,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 2008</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 6222</t>
+          <t>0; 6313</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1015; 9696</t>
+          <t>1014; 9530</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 4549</t>
+          <t>0; 4437</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 4625</t>
+          <t>0; 5669</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 1972</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 4535</t>
+          <t>0; 5033</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>988; 9347</t>
+          <t>982; 8534</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1009; 9710</t>
+          <t>1007; 9481</t>
         </is>
       </c>
     </row>
@@ -1906,47 +1906,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 4361</t>
+          <t>0; 4449</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1799; 9911</t>
+          <t>1874; 10487</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 5426</t>
+          <t>0; 5110</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 6749</t>
+          <t>0; 5985</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2058; 11691</t>
+          <t>2022; 11484</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2054; 11562</t>
+          <t>2027; 11538</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>877; 7469</t>
+          <t>878; 8343</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>5067; 18389</t>
+          <t>5031; 19185</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3005; 13392</t>
+          <t>2894; 12632</t>
         </is>
       </c>
     </row>
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 5789</t>
+          <t>0; 6502</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>9290; 24976</t>
+          <t>9346; 26343</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>5209; 18585</t>
+          <t>5085; 18973</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1878; 10719</t>
+          <t>1050; 10784</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>12289; 29755</t>
+          <t>12338; 30853</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>5172; 18929</t>
+          <t>5318; 19067</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2909; 13638</t>
+          <t>2875; 13372</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>25836; 49672</t>
+          <t>25363; 50094</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>12635; 31076</t>
+          <t>13685; 32176</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P02E$ssociales-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P02E$ssociales-Habitat-trans_dic.xlsx
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,74</t>
+          <t>0,0; 3,77</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,95; 5,62</t>
+          <t>0,96; 5,71</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,68; 6,22</t>
+          <t>0,66; 5,83</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,64</t>
+          <t>0,0; 2,84</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,66; 3,66</t>
+          <t>0,65; 3,38</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,39</t>
+          <t>0,0; 3,15</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,28; 2,37</t>
+          <t>0,28; 2,62</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,98; 3,46</t>
+          <t>1,0; 3,77</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,57; 3,42</t>
+          <t>0,56; 3,49</t>
         </is>
       </c>
     </row>
@@ -793,12 +793,12 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,37; 3,36</t>
+          <t>0,37; 3,33</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,54</t>
+          <t>0,0; 2,93</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -808,12 +808,12 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,89; 3,35</t>
+          <t>0,84; 3,35</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,27; 2,63</t>
+          <t>0,3; 2,46</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -823,12 +823,12 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,84; 2,89</t>
+          <t>0,86; 2,76</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,33; 2,04</t>
+          <t>0,3; 2,01</t>
         </is>
       </c>
     </row>
@@ -903,42 +903,42 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,86</t>
+          <t>0,0; 3,21</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,62; 5,81</t>
+          <t>0,62; 6,02</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,25</t>
+          <t>0,0; 2,32</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
+          <t>0,0; 2,06</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
           <t>0,0; 1,6</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 1,55</t>
-        </is>
-      </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,48</t>
+          <t>0,17; 1,47</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,24; 2,27</t>
+          <t>0,24; 2,29</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,61</t>
+          <t>0,0; 2,65</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,72; 4,01</t>
+          <t>0,71; 4,11</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,63</t>
+          <t>0,0; 2,09</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,12</t>
+          <t>0,0; 2,44</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,5; 2,83</t>
+          <t>0,51; 2,93</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,67; 3,82</t>
+          <t>0,67; 4,07</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,84</t>
+          <t>0,19; 1,88</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,75; 2,87</t>
+          <t>0,75; 2,7</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,58; 2,54</t>
+          <t>0,44; 2,73</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,04</t>
+          <t>0,0; 0,99</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,95; 2,67</t>
+          <t>1,0; 2,63</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,67; 2,51</t>
+          <t>0,66; 2,51</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,1; 1,07</t>
+          <t>0,19; 1,1</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,81; 2,03</t>
+          <t>0,79; 1,92</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,48; 1,72</t>
+          <t>0,45; 1,67</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,18; 0,82</t>
+          <t>0,17; 0,83</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,01; 2,0</t>
+          <t>1,02; 1,97</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,73; 1,72</t>
+          <t>0,7; 1,75</t>
         </is>
       </c>
     </row>
@@ -1417,47 +1417,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 4908</t>
+          <t>0; 4952</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1887; 11163</t>
+          <t>1910; 11347</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1087; 9982</t>
+          <t>1060; 9358</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 8006</t>
+          <t>0; 6244</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1961; 10923</t>
+          <t>1928; 10087</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 6664</t>
+          <t>0; 6198</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>970; 8335</t>
+          <t>966; 9205</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>4890; 17205</t>
+          <t>4969; 18721</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2020; 12216</t>
+          <t>2000; 12453</t>
         </is>
       </c>
     </row>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1123; 10217</t>
+          <t>1112; 10111</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 6040</t>
+          <t>0; 6963</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4077; 15358</t>
+          <t>3827; 15356</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>956; 9432</t>
+          <t>1062; 8819</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -1615,12 +1615,12 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6374; 22028</t>
+          <t>6541; 21011</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1982; 12134</t>
+          <t>1811; 12001</t>
         </is>
       </c>
     </row>
@@ -1748,22 +1748,22 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 6313</t>
+          <t>0; 7082</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1014; 9530</t>
+          <t>1018; 9869</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 4437</t>
+          <t>0; 4575</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 5669</t>
+          <t>0; 7304</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1773,17 +1773,17 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 5033</t>
+          <t>0; 5197</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>982; 8534</t>
+          <t>986; 8454</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1007; 9481</t>
+          <t>1015; 9567</t>
         </is>
       </c>
     </row>
@@ -1906,47 +1906,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 4449</t>
+          <t>0; 4512</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1874; 10487</t>
+          <t>1854; 10758</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 5110</t>
+          <t>0; 4071</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 5985</t>
+          <t>0; 6876</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2022; 11484</t>
+          <t>2080; 11880</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2027; 11538</t>
+          <t>2014; 12291</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>878; 8343</t>
+          <t>881; 8499</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>5031; 19185</t>
+          <t>5034; 18034</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2894; 12632</t>
+          <t>2208; 13561</t>
         </is>
       </c>
     </row>
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 6502</t>
+          <t>0; 6168</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>9346; 26343</t>
+          <t>9871; 25870</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>5085; 18973</t>
+          <t>5009; 19007</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1050; 10784</t>
+          <t>1897; 11091</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>12338; 30853</t>
+          <t>12014; 29190</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>5318; 19067</t>
+          <t>5034; 18590</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2875; 13372</t>
+          <t>2810; 13528</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>25363; 50094</t>
+          <t>25513; 49172</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>13685; 32176</t>
+          <t>12998; 32692</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P02E$ssociales-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P02E$ssociales-Habitat-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con ayuda al cuidado por parte de, al menos, una persona externa que es profesional de los servicios Sociales o sanitarios (tasa de respuesta: 96,71%)</t>
+          <t>Población con ayuda al cuidado por parte de, al menos, una persona externa que es profesional de los servicios Sociales o sanitarios (tasa de respuesta: 96,71%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1210,7 +1210,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con ayuda al cuidado por parte de, al menos, una persona externa que es profesional de los servicios Sociales o sanitarios (tasa de respuesta: 96,71%)</t>
+          <t>Población con ayuda al cuidado por parte de, al menos, una persona externa que es profesional de los servicios Sociales o sanitarios (tasa de respuesta: 96,71%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
